--- a/output/biophysical_models/biophysical_glmm_summary.xlsx
+++ b/output/biophysical_models/biophysical_glmm_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10329"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/helenkilleen/Desktop/CODING/seabirds-northern-ecosystems/output/biophysical_models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF246715-7303-6647-9A6E-BB5DD0B05674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A08A3AF9-AD92-FE42-B34F-14AC8606FD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="19000" xr2:uid="{2856326F-372B-C744-B3A9-BFD58621E6D8}"/>
   </bookViews>
@@ -35,29 +35,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="43">
   <si>
     <t>Arctic</t>
   </si>
   <si>
-    <t>Cold Temperate Northeast Pacific</t>
-  </si>
-  <si>
-    <t>Cold Temperate Northwest Atlantic</t>
-  </si>
-  <si>
-    <t>Cold Temperate Northwest Pacific</t>
-  </si>
-  <si>
     <t>Hawaii</t>
   </si>
   <si>
     <t>Northern European Seas</t>
   </si>
   <si>
-    <t>Warm Temperate Northeast Pacific</t>
-  </si>
-  <si>
     <t>pre breeding</t>
   </si>
   <si>
@@ -76,97 +64,106 @@
     <t>ML temperature</t>
   </si>
   <si>
-    <t xml:space="preserve"> -0.09 - 0.04</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -0.71 - -0.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -0.54 - -0.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -0.14 - 0.11</t>
-  </si>
-  <si>
-    <t>95% CI Temperature</t>
-  </si>
-  <si>
-    <t>95% CI Stratification</t>
-  </si>
-  <si>
     <t>Covariance</t>
   </si>
   <si>
-    <t>-0.20 - 0.02</t>
-  </si>
-  <si>
-    <t>-0.07 - 0.13</t>
-  </si>
-  <si>
-    <t>-0.15 - 0.06</t>
-  </si>
-  <si>
-    <t>-0.10 - 0.10</t>
-  </si>
-  <si>
-    <t>-0.06 - 0.07</t>
-  </si>
-  <si>
-    <t>-0.02 - 0.12</t>
-  </si>
-  <si>
-    <t>-0.06 - 0.06</t>
-  </si>
-  <si>
-    <t>0.00 - 0.18</t>
-  </si>
-  <si>
-    <t>-0.21 - -0.03</t>
-  </si>
-  <si>
-    <t>0.03 - 0.21</t>
-  </si>
-  <si>
-    <t>-0.21 - -0.05</t>
-  </si>
-  <si>
-    <t>-0.12 - 0.01</t>
-  </si>
-  <si>
-    <t>-0.01 - 0.11</t>
-  </si>
-  <si>
-    <t>-0.09 - 0.04</t>
-  </si>
-  <si>
-    <t>-0.11 - 0.01</t>
-  </si>
-  <si>
-    <t>-0.65 - -0.20</t>
-  </si>
-  <si>
-    <t>-0.48 - -0.01</t>
-  </si>
-  <si>
-    <t>-0.09 - 0.20</t>
-  </si>
-  <si>
-    <t>-0.03 - 0.29</t>
-  </si>
-  <si>
-    <t>-0.09 - 0.16</t>
-  </si>
-  <si>
-    <t>0.08 - 0.47</t>
-  </si>
-  <si>
-    <t>0.24 - 0.64</t>
-  </si>
-  <si>
-    <t>-0.05 - 0.40</t>
-  </si>
-  <si>
-    <t>-0.38 - 0.17</t>
+    <t>90% CI Temperature</t>
+  </si>
+  <si>
+    <t>90% CI Stratification</t>
+  </si>
+  <si>
+    <t>-0.19 : 0.00</t>
+  </si>
+  <si>
+    <t>-0.05 : 0.11</t>
+  </si>
+  <si>
+    <t>-0.13 : 0.04</t>
+  </si>
+  <si>
+    <t>-0.08 : 0.08</t>
+  </si>
+  <si>
+    <t>-0.08 : 0.03</t>
+  </si>
+  <si>
+    <t>-0.05 : 0.06</t>
+  </si>
+  <si>
+    <t>-0.01 : 0.11</t>
+  </si>
+  <si>
+    <t>-0.05 : 0.05</t>
+  </si>
+  <si>
+    <t>-0.01 : 0.17</t>
+  </si>
+  <si>
+    <t>-0.19 : -0.05</t>
+  </si>
+  <si>
+    <t>-0.20 : -0.06</t>
+  </si>
+  <si>
+    <t>-0.11 : 0.00</t>
+  </si>
+  <si>
+    <t>0.04 : 0.20</t>
+  </si>
+  <si>
+    <t>0.00 : 0.10</t>
+  </si>
+  <si>
+    <t>-0.10 : 0.00</t>
+  </si>
+  <si>
+    <t>-0.67 : -0.27</t>
+  </si>
+  <si>
+    <t>-0.62 : -0.24</t>
+  </si>
+  <si>
+    <t>-0.49 : -0.05</t>
+  </si>
+  <si>
+    <t>-0.44 : -0.05</t>
+  </si>
+  <si>
+    <t>-0.06 : 0.18</t>
+  </si>
+  <si>
+    <t>-0.12 : 0.08</t>
+  </si>
+  <si>
+    <t>0.00 : 0.26</t>
+  </si>
+  <si>
+    <t>-0.07 : 0.14</t>
+  </si>
+  <si>
+    <t>0.11 : 0.44</t>
+  </si>
+  <si>
+    <t>0.28 : 0.61</t>
+  </si>
+  <si>
+    <t>-0.33 : 0.12</t>
+  </si>
+  <si>
+    <t>-0.02 : 0.36</t>
+  </si>
+  <si>
+    <t>Northwest Atlantic</t>
+  </si>
+  <si>
+    <t>Cold Northeast Pacific</t>
+  </si>
+  <si>
+    <t>Warm Northeast Pacific</t>
+  </si>
+  <si>
+    <t>Northwest Pacific</t>
   </si>
 </sst>
 </file>
@@ -240,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -281,6 +278,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -610,25 +610,25 @@
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="12" t="s">
         <v>11</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -636,7 +636,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C2" s="4">
         <v>-0.38848402999999998</v>
@@ -645,13 +645,13 @@
         <v>-0.09</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F2" s="7">
         <v>0.03</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -659,7 +659,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4">
         <v>0.29847304800000002</v>
@@ -668,21 +668,21 @@
         <v>-0.04</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F3" s="7">
         <v>0</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4">
         <v>1.0097261E-2</v>
@@ -691,21 +691,21 @@
         <v>-0.03</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F4" s="7">
         <v>0</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C5" s="4">
         <v>0.67213442980000004</v>
@@ -714,21 +714,21 @@
         <v>0.05</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F5" s="7">
         <v>0</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C6" s="4">
         <v>-9.4241850000000002E-2</v>
@@ -737,21 +737,21 @@
         <v>0.09</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F6" s="7">
         <v>-0.12</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C7" s="4">
         <v>0.29801315</v>
@@ -759,22 +759,22 @@
       <c r="D7" s="7">
         <v>0.12</v>
       </c>
-      <c r="E7" s="12" t="s">
-        <v>29</v>
+      <c r="E7" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="F7" s="7">
         <v>-0.13</v>
       </c>
-      <c r="G7" s="16" t="s">
-        <v>30</v>
+      <c r="G7" s="12" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C8" s="4">
         <v>0.70805233999999995</v>
@@ -783,21 +783,21 @@
         <v>-0.06</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F8" s="7">
         <v>-0.02</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C9" s="4">
         <v>0.74343210999999998</v>
@@ -806,21 +806,21 @@
         <v>0.05</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F9" s="7">
         <v>-0.05</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C10" s="4">
         <v>0.77049650000000003</v>
@@ -829,21 +829,21 @@
         <v>-0.47</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F10" s="7">
         <v>-0.43</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C11" s="4">
         <v>0.79669900000000005</v>
@@ -852,21 +852,21 @@
         <v>-0.27</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F11" s="7">
         <v>-0.25</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>3</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>7</v>
       </c>
       <c r="C12" s="4">
         <v>9.2184420000000003E-2</v>
@@ -875,21 +875,21 @@
         <v>0.06</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F12" s="7">
         <v>-0.02</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C13" s="4">
         <v>0.10509804</v>
@@ -898,21 +898,21 @@
         <v>0.13</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F13" s="7">
         <v>0.03</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" s="4">
         <v>0.82484632000000002</v>
@@ -921,21 +921,21 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F14" s="7">
         <v>0.44</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>4</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>8</v>
       </c>
       <c r="C15" s="4">
         <v>0.73420410000000003</v>
@@ -944,13 +944,13 @@
         <v>-0.1</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F15" s="7">
         <v>0.17</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
